--- a/artfynd/A 46508-2025 artfynd.xlsx
+++ b/artfynd/A 46508-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56125120</v>
+        <v>70832249</v>
       </c>
       <c r="B2" t="n">
-        <v>95572</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221063</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>O om Marma By, Upl</t>
+          <t>N Militärvägen, strax utanför Marma skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634211.9559932924</v>
+        <v>634163</v>
       </c>
       <c r="R2" t="n">
-        <v>6706359.851034942</v>
+        <v>6706362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spridda tuvor</t>
+          <t>2018-04-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,74 +760,67 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tommy Löfgren, Andreas Press</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67979998</v>
+        <v>112025123</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SO om Marma Skjutfält, Upl</t>
+          <t>norr Finnmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634217.8619554716</v>
+        <v>634265</v>
       </c>
       <c r="R3" t="n">
-        <v>6706373.889803199</v>
+        <v>6706436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,27 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>örtgranskog med björk, asp och ädellöv</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,33 +858,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67980382</v>
+        <v>104765681</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,43 +888,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SO om Marma Skjutfält, Upl</t>
+          <t>NBI SO om Marma skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634340.9739629312</v>
+        <v>634254</v>
       </c>
       <c r="R4" t="n">
-        <v>6706346.871330771</v>
+        <v>6706438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,22 +951,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>örtgranskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70832249</v>
+        <v>61999640</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,34 +999,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Militärvägen, strax utanför Marma skjutfält, Upl</t>
+          <t>Äldre skog 1 km SO Marma läger, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634162.934547046</v>
+        <v>633931</v>
       </c>
       <c r="R5" t="n">
-        <v>6706361.981274038</v>
+        <v>6706427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,22 +1062,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,74 +1087,74 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Press, Tommy Löfgren</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81678822</v>
+        <v>70832241</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>O syddelen av Marma skjutfält, Upl</t>
+          <t>N Militärvägen, strax utanför Marma skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633888.169782432</v>
+        <v>633931</v>
       </c>
       <c r="R6" t="n">
-        <v>6706359.205715246</v>
+        <v>6706425</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,22 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1198,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1272,67 +1210,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70832241</v>
+        <v>67980270</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Militärvägen, strax utanför Marma skjutfält, Upl</t>
+          <t>SO om Marma Skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633931.2170612636</v>
+        <v>633758</v>
       </c>
       <c r="R7" t="n">
-        <v>6706424.960913393</v>
+        <v>6706446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,22 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,7 +1304,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1398,59 +1316,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61999640</v>
+        <v>67980382</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Äldre skog 1 km SO Marma läger, Upl</t>
+          <t>SO om Marma Skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633931.1440751178</v>
+        <v>634341</v>
       </c>
       <c r="R8" t="n">
-        <v>6706426.932404167</v>
+        <v>6706347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,27 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,6 +1419,1086 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>70832248</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>N Militärvägen, strax utanför Marma skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>634174</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706443</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Press</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>73575740</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gammalt skogsskifte SO om Marma skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>634174</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706444</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81678822</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>O syddelen av Marma skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>633888</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706359</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-08-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>92765381</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N om Militärvägen, strax utanför Marma skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>634173</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706443</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C-Älv-0466</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>92765395</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Marma skjutfält, O om syddelen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>633889</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6706359</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>C-Älv-0453</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-08-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-08-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>92765396</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SO om Marma Skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>634340</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706347</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C-Älv-0452</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>56125120</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>O om Marma By, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634212</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6706360</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2014-11-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2014-11-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>spridda tuvor</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>70832247</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Militärvägen, strax utanför Marma skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>634244</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6706435</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Press</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73575776</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gammalt skogsskifte SO om Marma skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>634245</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706435</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>67979998</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SO om Marma Skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>634218</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6706374</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>örtgranskog med björk, asp och ädellöv</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46508-2025 artfynd.xlsx
+++ b/artfynd/A 46508-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70832249</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025123</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104765681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999640</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70832241</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980382</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70832248</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73575740</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678822</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92765381</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92765395</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92765396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56125120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70832247</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,6 +2468,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73575776</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2499,8 +2584,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67979998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>